--- a/output/RESULT 10.07.24.xlsx
+++ b/output/RESULT 10.07.24.xlsx
@@ -500,17 +500,36 @@
           <t>Товар A</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Товар</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>ТОВАР A</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1 шт</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>SKU-1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Товар A</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>MATCH</t>

--- a/output/RESULT 10.07.24.xlsx
+++ b/output/RESULT 10.07.24.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,11 @@
           <t>SVO Match Engine</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>????????</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -438,6 +443,9 @@
         <is>
           <t>10.07.24</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
